--- a/estimation/notsensor/DenseModel/Dense_1st_torch_optimized/IWALQQ_1st_correction/angle/1_fold/56.xlsx
+++ b/estimation/notsensor/DenseModel/Dense_1st_torch_optimized/IWALQQ_1st_correction/angle/1_fold/56.xlsx
@@ -426,13 +426,13 @@
         <v>-21.54237449347184</v>
       </c>
       <c r="E2">
-        <v>-23.97920934144173</v>
+        <v>-25.15774923041195</v>
       </c>
       <c r="F2">
-        <v>-1.323117436675643</v>
+        <v>-2.217528087398145</v>
       </c>
       <c r="G2">
-        <v>-13.89577769248031</v>
+        <v>-15.63943706219614</v>
       </c>
     </row>
     <row r="3" spans="1:7">
@@ -449,13 +449,13 @@
         <v>-21.48477989339583</v>
       </c>
       <c r="E3">
-        <v>-24.57538747302554</v>
+        <v>-25.0738818917899</v>
       </c>
       <c r="F3">
-        <v>-1.169679771022494</v>
+        <v>-2.397056841137271</v>
       </c>
       <c r="G3">
-        <v>-15.19428786680358</v>
+        <v>-15.56169386602466</v>
       </c>
     </row>
     <row r="4" spans="1:7">
@@ -472,13 +472,13 @@
         <v>-21.37442129303769</v>
       </c>
       <c r="E4">
-        <v>-24.30789957034047</v>
+        <v>-25.99321192856106</v>
       </c>
       <c r="F4">
-        <v>-1.038805176686797</v>
+        <v>-2.262793395756721</v>
       </c>
       <c r="G4">
-        <v>-13.97783287421669</v>
+        <v>-15.13064428408386</v>
       </c>
     </row>
     <row r="5" spans="1:7">
@@ -495,13 +495,13 @@
         <v>-21.2050511395876</v>
       </c>
       <c r="E5">
-        <v>-26.11387764696945</v>
+        <v>-26.46340338477748</v>
       </c>
       <c r="F5">
-        <v>-1.36346804123341</v>
+        <v>-2.152687628944014</v>
       </c>
       <c r="G5">
-        <v>-14.08624496426397</v>
+        <v>-14.54427549234984</v>
       </c>
     </row>
     <row r="6" spans="1:7">
@@ -518,13 +518,13 @@
         <v>-20.97672103514013</v>
       </c>
       <c r="E6">
-        <v>-24.41736637252789</v>
+        <v>-26.32909790265799</v>
       </c>
       <c r="F6">
-        <v>-1.180694572377519</v>
+        <v>-2.265512097572709</v>
       </c>
       <c r="G6">
-        <v>-13.74664920284553</v>
+        <v>-14.95703927600448</v>
       </c>
     </row>
     <row r="7" spans="1:7">
@@ -541,13 +541,13 @@
         <v>-20.6798743960933</v>
       </c>
       <c r="E7">
-        <v>-24.62892762121823</v>
+        <v>-27.16211069636895</v>
       </c>
       <c r="F7">
-        <v>-1.367389532518263</v>
+        <v>-2.018916233800727</v>
       </c>
       <c r="G7">
-        <v>-13.30662969776608</v>
+        <v>-14.1196765083923</v>
       </c>
     </row>
     <row r="8" spans="1:7">
@@ -564,13 +564,13 @@
         <v>-20.32949833910278</v>
       </c>
       <c r="E8">
-        <v>-25.91604220299635</v>
+        <v>-27.67373316128154</v>
       </c>
       <c r="F8">
-        <v>-1.546481736636113</v>
+        <v>-2.32847050528768</v>
       </c>
       <c r="G8">
-        <v>-13.79460411025465</v>
+        <v>-13.90973495247388</v>
       </c>
     </row>
     <row r="9" spans="1:7">
@@ -587,13 +587,13 @@
         <v>-19.95701981891185</v>
       </c>
       <c r="E9">
-        <v>-26.46990627345249</v>
+        <v>-28.16889009470224</v>
       </c>
       <c r="F9">
-        <v>-0.872924604276196</v>
+        <v>-1.932409825926375</v>
       </c>
       <c r="G9">
-        <v>-12.54804798235194</v>
+        <v>-14.03962255143442</v>
       </c>
     </row>
     <row r="10" spans="1:7">
@@ -610,13 +610,13 @@
         <v>-19.58110395791656</v>
       </c>
       <c r="E10">
-        <v>-27.43125149206682</v>
+        <v>-29.01395315774761</v>
       </c>
       <c r="F10">
-        <v>-1.391937372132823</v>
+        <v>-2.052214946658462</v>
       </c>
       <c r="G10">
-        <v>-11.37158934569775</v>
+        <v>-13.09663186257348</v>
       </c>
     </row>
     <row r="11" spans="1:7">
@@ -633,13 +633,13 @@
         <v>-19.24164859707314</v>
       </c>
       <c r="E11">
-        <v>-26.57065576317514</v>
+        <v>-29.15225728241587</v>
       </c>
       <c r="F11">
-        <v>-1.093126197492777</v>
+        <v>-2.088340049094548</v>
       </c>
       <c r="G11">
-        <v>-12.75150749010446</v>
+        <v>-12.68325397272131</v>
       </c>
     </row>
     <row r="12" spans="1:7">
@@ -656,13 +656,13 @@
         <v>-18.98354395104441</v>
       </c>
       <c r="E12">
-        <v>-27.00936526809023</v>
+        <v>-29.5935865095444</v>
       </c>
       <c r="F12">
-        <v>-1.012058849985207</v>
+        <v>-1.966845887228153</v>
       </c>
       <c r="G12">
-        <v>-11.36907333108791</v>
+        <v>-12.10756334562421</v>
       </c>
     </row>
     <row r="13" spans="1:7">
@@ -679,13 +679,13 @@
         <v>-18.82553572808212</v>
       </c>
       <c r="E13">
-        <v>-29.28894021338939</v>
+        <v>-30.57730465399363</v>
       </c>
       <c r="F13">
-        <v>-1.025859450915846</v>
+        <v>-1.927264835987587</v>
       </c>
       <c r="G13">
-        <v>-11.58525526534785</v>
+        <v>-11.78487785082037</v>
       </c>
     </row>
     <row r="14" spans="1:7">
@@ -702,13 +702,13 @@
         <v>-18.79313168342818</v>
       </c>
       <c r="E14">
-        <v>-28.46093591193091</v>
+        <v>-31.1941824402665</v>
       </c>
       <c r="F14">
-        <v>-0.7855210745046117</v>
+        <v>-1.611347874479731</v>
       </c>
       <c r="G14">
-        <v>-11.4294311973599</v>
+        <v>-11.82366089181293</v>
       </c>
     </row>
     <row r="15" spans="1:7">
@@ -725,13 +725,13 @@
         <v>-18.90045808006811</v>
       </c>
       <c r="E15">
-        <v>-30.89004786167435</v>
+        <v>-31.5125817119828</v>
       </c>
       <c r="F15">
-        <v>0.1262007982015941</v>
+        <v>-1.284637285713398</v>
       </c>
       <c r="G15">
-        <v>-10.31099649237252</v>
+        <v>-11.51586954139027</v>
       </c>
     </row>
     <row r="16" spans="1:7">
@@ -748,13 +748,13 @@
         <v>-19.12525461228545</v>
       </c>
       <c r="E16">
-        <v>-29.05102777444841</v>
+        <v>-32.28405707240353</v>
       </c>
       <c r="F16">
-        <v>-0.04156265331557014</v>
+        <v>-1.438520613029254</v>
       </c>
       <c r="G16">
-        <v>-10.4948774338058</v>
+        <v>-11.05584606488976</v>
       </c>
     </row>
     <row r="17" spans="1:7">
@@ -771,13 +771,13 @@
         <v>-19.44741580541627</v>
       </c>
       <c r="E17">
-        <v>-30.75562237499366</v>
+        <v>-32.2046887727081</v>
       </c>
       <c r="F17">
-        <v>-0.4494515908214495</v>
+        <v>-1.004535617232981</v>
       </c>
       <c r="G17">
-        <v>-10.38503353281278</v>
+        <v>-11.07183599984444</v>
       </c>
     </row>
     <row r="18" spans="1:7">
@@ -794,13 +794,13 @@
         <v>-19.84072957806061</v>
       </c>
       <c r="E18">
-        <v>-31.94854243317524</v>
+        <v>-34.36405763971065</v>
       </c>
       <c r="F18">
-        <v>0.5213063699474715</v>
+        <v>-1.052332416374513</v>
       </c>
       <c r="G18">
-        <v>-9.790628391782178</v>
+        <v>-10.50685829811242</v>
       </c>
     </row>
     <row r="19" spans="1:7">
@@ -817,13 +817,13 @@
         <v>-20.25628481541808</v>
       </c>
       <c r="E19">
-        <v>-30.97555450788719</v>
+        <v>-34.31771550095316</v>
       </c>
       <c r="F19">
-        <v>0.3525157428508359</v>
+        <v>-1.104276022734459</v>
       </c>
       <c r="G19">
-        <v>-9.540675582476124</v>
+        <v>-10.15011391080056</v>
       </c>
     </row>
     <row r="20" spans="1:7">
@@ -840,13 +840,13 @@
         <v>-20.65980345632731</v>
       </c>
       <c r="E20">
-        <v>-33.197072152171</v>
+        <v>-34.31145714987456</v>
       </c>
       <c r="F20">
-        <v>0.6365471862901332</v>
+        <v>-0.6131800647195774</v>
       </c>
       <c r="G20">
-        <v>-9.416993601128953</v>
+        <v>-10.22697484658582</v>
       </c>
     </row>
     <row r="21" spans="1:7">
@@ -863,13 +863,13 @@
         <v>-21.02214756426707</v>
       </c>
       <c r="E21">
-        <v>-32.2853929722358</v>
+        <v>-35.0488783857576</v>
       </c>
       <c r="F21">
-        <v>0.7136143476095852</v>
+        <v>-0.5368029334466574</v>
       </c>
       <c r="G21">
-        <v>-9.453912804982906</v>
+        <v>-10.29397697775513</v>
       </c>
     </row>
     <row r="22" spans="1:7">
@@ -886,13 +886,13 @@
         <v>-21.30326031033102</v>
       </c>
       <c r="E22">
-        <v>-33.74079470508697</v>
+        <v>-35.72343987394018</v>
       </c>
       <c r="F22">
-        <v>0.5597351621307434</v>
+        <v>-0.7589437347531924</v>
       </c>
       <c r="G22">
-        <v>-8.560022472287674</v>
+        <v>-10.41555014159378</v>
       </c>
     </row>
     <row r="23" spans="1:7">
@@ -909,13 +909,13 @@
         <v>-21.48404958585135</v>
       </c>
       <c r="E23">
-        <v>-34.2505582314194</v>
+        <v>-36.42650357752704</v>
       </c>
       <c r="F23">
-        <v>0.908842320366567</v>
+        <v>-0.3535349292512948</v>
       </c>
       <c r="G23">
-        <v>-9.418033112428285</v>
+        <v>-10.05716372369444</v>
       </c>
     </row>
     <row r="24" spans="1:7">
@@ -932,13 +932,13 @@
         <v>-21.55510313413708</v>
       </c>
       <c r="E24">
-        <v>-34.96780511559828</v>
+        <v>-36.15887529214773</v>
       </c>
       <c r="F24">
-        <v>1.608168305892771</v>
+        <v>-0.4414338227297531</v>
       </c>
       <c r="G24">
-        <v>-9.02985840576658</v>
+        <v>-9.911516272694206</v>
       </c>
     </row>
     <row r="25" spans="1:7">
@@ -955,13 +955,13 @@
         <v>-21.50209975819078</v>
       </c>
       <c r="E25">
-        <v>-34.97040672391569</v>
+        <v>-36.59921504770558</v>
       </c>
       <c r="F25">
-        <v>1.299536835692537</v>
+        <v>-0.3560399122773605</v>
       </c>
       <c r="G25">
-        <v>-9.100555105757717</v>
+        <v>-10.09624802433108</v>
       </c>
     </row>
     <row r="26" spans="1:7">
@@ -978,13 +978,13 @@
         <v>-21.33326979464829</v>
       </c>
       <c r="E26">
-        <v>-35.00325401013033</v>
+        <v>-36.53342990579615</v>
       </c>
       <c r="F26">
-        <v>0.5993849678657417</v>
+        <v>-0.3746442157768345</v>
       </c>
       <c r="G26">
-        <v>-9.547644280836291</v>
+        <v>-10.27926822392415</v>
       </c>
     </row>
     <row r="27" spans="1:7">
@@ -1001,13 +1001,13 @@
         <v>-21.06524856170505</v>
       </c>
       <c r="E27">
-        <v>-35.53802150569612</v>
+        <v>-35.9865872342889</v>
       </c>
       <c r="F27">
-        <v>0.8746489707138091</v>
+        <v>-0.444632149271962</v>
       </c>
       <c r="G27">
-        <v>-9.595038050776497</v>
+        <v>-9.77649236232949</v>
       </c>
     </row>
     <row r="28" spans="1:7">
@@ -1024,13 +1024,13 @@
         <v>-20.70850324776925</v>
       </c>
       <c r="E28">
-        <v>-34.85131917869898</v>
+        <v>-36.96353531009667</v>
       </c>
       <c r="F28">
-        <v>1.406790533537406</v>
+        <v>-0.3378688449295505</v>
       </c>
       <c r="G28">
-        <v>-9.118677032039688</v>
+        <v>-10.16324353440931</v>
       </c>
     </row>
     <row r="29" spans="1:7">
@@ -1047,13 +1047,13 @@
         <v>-20.29175230526464</v>
       </c>
       <c r="E29">
-        <v>-34.36194284234907</v>
+        <v>-36.17145539294103</v>
       </c>
       <c r="F29">
-        <v>0.3620891849249898</v>
+        <v>-0.4953332045277085</v>
       </c>
       <c r="G29">
-        <v>-7.843024519392321</v>
+        <v>-9.882300708310137</v>
       </c>
     </row>
     <row r="30" spans="1:7">
@@ -1070,13 +1070,13 @@
         <v>-19.84331336425048</v>
       </c>
       <c r="E30">
-        <v>-35.09441898461574</v>
+        <v>-36.4697572970113</v>
       </c>
       <c r="F30">
-        <v>0.5671788716122997</v>
+        <v>-0.6844875874873645</v>
       </c>
       <c r="G30">
-        <v>-8.864771431359744</v>
+        <v>-9.619297728488277</v>
       </c>
     </row>
     <row r="31" spans="1:7">
@@ -1093,13 +1093,13 @@
         <v>-19.37949773082892</v>
       </c>
       <c r="E31">
-        <v>-34.72281920025733</v>
+        <v>-35.88477128893745</v>
       </c>
       <c r="F31">
-        <v>0.8776758252036384</v>
+        <v>-0.5174116809145237</v>
       </c>
       <c r="G31">
-        <v>-9.058699878504711</v>
+        <v>-9.313860175944038</v>
       </c>
     </row>
     <row r="32" spans="1:7">
@@ -1116,13 +1116,13 @@
         <v>-18.92911289224046</v>
       </c>
       <c r="E32">
-        <v>-34.49167003724681</v>
+        <v>-35.94133645776726</v>
       </c>
       <c r="F32">
-        <v>1.133656263281936</v>
+        <v>-0.7179470036212421</v>
       </c>
       <c r="G32">
-        <v>-9.127734684635133</v>
+        <v>-9.78594065929857</v>
       </c>
     </row>
     <row r="33" spans="1:7">
@@ -1139,13 +1139,13 @@
         <v>-18.51339118888968</v>
       </c>
       <c r="E33">
-        <v>-35.2213838103688</v>
+        <v>-35.32024719066725</v>
       </c>
       <c r="F33">
-        <v>0.1121210374562109</v>
+        <v>-0.5869895725452654</v>
       </c>
       <c r="G33">
-        <v>-7.658014681930151</v>
+        <v>-9.768351730848423</v>
       </c>
     </row>
     <row r="34" spans="1:7">
@@ -1162,13 +1162,13 @@
         <v>-18.1390530944317</v>
       </c>
       <c r="E34">
-        <v>-32.84711620933225</v>
+        <v>-34.50699212905176</v>
       </c>
       <c r="F34">
-        <v>0.993375557087451</v>
+        <v>-0.7209208425972923</v>
       </c>
       <c r="G34">
-        <v>-8.383408178313097</v>
+        <v>-10.25156888939706</v>
       </c>
     </row>
     <row r="35" spans="1:7">
@@ -1185,13 +1185,13 @@
         <v>-17.82239241638903</v>
       </c>
       <c r="E35">
-        <v>-33.69063506274101</v>
+        <v>-34.92864740085396</v>
       </c>
       <c r="F35">
-        <v>-0.1137167675690183</v>
+        <v>-0.5223321832871528</v>
       </c>
       <c r="G35">
-        <v>-8.6033376501235</v>
+        <v>-9.64958259908153</v>
       </c>
     </row>
     <row r="36" spans="1:7">
@@ -1208,13 +1208,13 @@
         <v>-17.56917125268334</v>
       </c>
       <c r="E36">
-        <v>-32.37213589185272</v>
+        <v>-34.70918170078323</v>
       </c>
       <c r="F36">
-        <v>0.6591326235274617</v>
+        <v>-0.6121255530158136</v>
       </c>
       <c r="G36">
-        <v>-7.719852362058197</v>
+        <v>-10.11209891637311</v>
       </c>
     </row>
     <row r="37" spans="1:7">
@@ -1231,13 +1231,13 @@
         <v>-17.37121263965172</v>
       </c>
       <c r="E37">
-        <v>-31.92686689233753</v>
+        <v>-33.96150799974681</v>
       </c>
       <c r="F37">
-        <v>0.1553394499624695</v>
+        <v>-0.6164239514689402</v>
       </c>
       <c r="G37">
-        <v>-8.373367293692487</v>
+        <v>-10.15668203315047</v>
       </c>
     </row>
     <row r="38" spans="1:7">
@@ -1254,13 +1254,13 @@
         <v>-17.22851120230698</v>
       </c>
       <c r="E38">
-        <v>-30.99198607582402</v>
+        <v>-33.44820094250337</v>
       </c>
       <c r="F38">
-        <v>0.5402801253085942</v>
+        <v>-0.4835977235322479</v>
       </c>
       <c r="G38">
-        <v>-9.340480272625317</v>
+        <v>-10.43741298433513</v>
       </c>
     </row>
     <row r="39" spans="1:7">
@@ -1277,13 +1277,13 @@
         <v>-17.13141059607124</v>
       </c>
       <c r="E39">
-        <v>-31.48753472224638</v>
+        <v>-32.74714788137592</v>
       </c>
       <c r="F39">
-        <v>0.6531700349621108</v>
+        <v>-0.5547544834327255</v>
       </c>
       <c r="G39">
-        <v>-8.322424618934182</v>
+        <v>-9.891080275080284</v>
       </c>
     </row>
     <row r="40" spans="1:7">
@@ -1300,13 +1300,13 @@
         <v>-17.06066853073521</v>
       </c>
       <c r="E40">
-        <v>-30.50474038649472</v>
+        <v>-33.01465842643103</v>
       </c>
       <c r="F40">
-        <v>0.01072803898614865</v>
+        <v>-0.3541429509249496</v>
       </c>
       <c r="G40">
-        <v>-8.505199838157344</v>
+        <v>-10.42911675721372</v>
       </c>
     </row>
     <row r="41" spans="1:7">
@@ -1323,13 +1323,13 @@
         <v>-17.00834306948995</v>
       </c>
       <c r="E41">
-        <v>-31.02176532089846</v>
+        <v>-32.48466167823232</v>
       </c>
       <c r="F41">
-        <v>0.3885422695659891</v>
+        <v>-0.1206228666061578</v>
       </c>
       <c r="G41">
-        <v>-8.48568417220334</v>
+        <v>-10.03513535367613</v>
       </c>
     </row>
     <row r="42" spans="1:7">
@@ -1346,13 +1346,13 @@
         <v>-16.96223895785921</v>
       </c>
       <c r="E42">
-        <v>-29.97306583867616</v>
+        <v>-31.94500569497525</v>
       </c>
       <c r="F42">
-        <v>0.8013732469969703</v>
+        <v>-0.06919284803594766</v>
       </c>
       <c r="G42">
-        <v>-8.944717795587604</v>
+        <v>-10.13790461885173</v>
       </c>
     </row>
     <row r="43" spans="1:7">
@@ -1369,13 +1369,13 @@
         <v>-16.90694451480242</v>
       </c>
       <c r="E43">
-        <v>-30.89286230827012</v>
+        <v>-31.64017825985993</v>
       </c>
       <c r="F43">
-        <v>0.2075067155211712</v>
+        <v>-0.08556304465007149</v>
       </c>
       <c r="G43">
-        <v>-9.634973161616726</v>
+        <v>-9.870061621451452</v>
       </c>
     </row>
     <row r="44" spans="1:7">
@@ -1392,13 +1392,13 @@
         <v>-16.84172058768986</v>
       </c>
       <c r="E44">
-        <v>-30.8310961870425</v>
+        <v>-30.98704098220764</v>
       </c>
       <c r="F44">
-        <v>1.204713619094078</v>
+        <v>-0.3089903005331541</v>
       </c>
       <c r="G44">
-        <v>-8.467068974636017</v>
+        <v>-10.63508234793947</v>
       </c>
     </row>
     <row r="45" spans="1:7">
@@ -1415,13 +1415,13 @@
         <v>-16.76571769612574</v>
       </c>
       <c r="E45">
-        <v>-28.40519492537049</v>
+        <v>-30.26990051716794</v>
       </c>
       <c r="F45">
-        <v>0.8899770811352111</v>
+        <v>0.09698096643524437</v>
       </c>
       <c r="G45">
-        <v>-8.059967879126301</v>
+        <v>-10.34942861553792</v>
       </c>
     </row>
     <row r="46" spans="1:7">
@@ -1438,13 +1438,13 @@
         <v>-16.67596582746208</v>
       </c>
       <c r="E46">
-        <v>-28.53513495854659</v>
+        <v>-29.31079915742441</v>
       </c>
       <c r="F46">
-        <v>1.212745469431622</v>
+        <v>-0.2571875166316843</v>
       </c>
       <c r="G46">
-        <v>-8.567332156838386</v>
+        <v>-10.7603964282375</v>
       </c>
     </row>
     <row r="47" spans="1:7">
@@ -1461,13 +1461,13 @@
         <v>-16.58191611548855</v>
       </c>
       <c r="E47">
-        <v>-27.59316708021108</v>
+        <v>-28.80739587283574</v>
       </c>
       <c r="F47">
-        <v>1.399934964911837</v>
+        <v>0.02838220507461171</v>
       </c>
       <c r="G47">
-        <v>-8.890663208022385</v>
+        <v>-11.03489693271725</v>
       </c>
     </row>
     <row r="48" spans="1:7">
@@ -1484,13 +1484,13 @@
         <v>-16.49101543878633</v>
       </c>
       <c r="E48">
-        <v>-26.50928135494918</v>
+        <v>-29.90839017289862</v>
       </c>
       <c r="F48">
-        <v>0.8220310732879844</v>
+        <v>0.02726805091784637</v>
       </c>
       <c r="G48">
-        <v>-10.11235051783409</v>
+        <v>-11.28638252460799</v>
       </c>
     </row>
     <row r="49" spans="1:7">
@@ -1507,13 +1507,13 @@
         <v>-16.40644453734368</v>
       </c>
       <c r="E49">
-        <v>-27.32529878570936</v>
+        <v>-28.75675847648197</v>
       </c>
       <c r="F49">
-        <v>1.182922586196034</v>
+        <v>-0.2231697808683198</v>
       </c>
       <c r="G49">
-        <v>-8.217198928968447</v>
+        <v>-11.0693034325069</v>
       </c>
     </row>
     <row r="50" spans="1:7">
@@ -1530,13 +1530,13 @@
         <v>-16.34104117151434</v>
       </c>
       <c r="E50">
-        <v>-25.9815420510433</v>
+        <v>-28.26587189405051</v>
       </c>
       <c r="F50">
-        <v>1.190813614075102</v>
+        <v>0.02154486053190459</v>
       </c>
       <c r="G50">
-        <v>-10.15167317774955</v>
+        <v>-11.60334077562889</v>
       </c>
     </row>
     <row r="51" spans="1:7">
@@ -1553,13 +1553,13 @@
         <v>-16.30319178339512</v>
       </c>
       <c r="E51">
-        <v>-26.15002845497268</v>
+        <v>-27.10968455278215</v>
       </c>
       <c r="F51">
-        <v>1.056152552341209</v>
+        <v>0.01735000800412789</v>
       </c>
       <c r="G51">
-        <v>-10.44620910383297</v>
+        <v>-11.3655575317252</v>
       </c>
     </row>
     <row r="52" spans="1:7">
@@ -1576,13 +1576,13 @@
         <v>-16.29409320350327</v>
       </c>
       <c r="E52">
-        <v>-26.51015987890667</v>
+        <v>-27.65525698733024</v>
       </c>
       <c r="F52">
-        <v>0.8386994821671161</v>
+        <v>-0.1176382588538711</v>
       </c>
       <c r="G52">
-        <v>-10.89674124627239</v>
+        <v>-11.54288028244518</v>
       </c>
     </row>
     <row r="53" spans="1:7">
@@ -1599,13 +1599,13 @@
         <v>-16.32263407004152</v>
       </c>
       <c r="E53">
-        <v>-24.78038696287877</v>
+        <v>-26.94342162959054</v>
       </c>
       <c r="F53">
-        <v>0.9764851457443691</v>
+        <v>-0.09746254239128639</v>
       </c>
       <c r="G53">
-        <v>-10.24385531829056</v>
+        <v>-11.43008999592221</v>
       </c>
     </row>
     <row r="54" spans="1:7">
@@ -1622,13 +1622,13 @@
         <v>-16.39218613340881</v>
       </c>
       <c r="E54">
-        <v>-25.50416390657671</v>
+        <v>-26.81335932761623</v>
       </c>
       <c r="F54">
-        <v>1.346223622514317</v>
+        <v>0.04301697197987057</v>
       </c>
       <c r="G54">
-        <v>-9.908612924256264</v>
+        <v>-12.08866675168605</v>
       </c>
     </row>
     <row r="55" spans="1:7">
@@ -1645,13 +1645,13 @@
         <v>-16.49833937897738</v>
       </c>
       <c r="E55">
-        <v>-25.64050267352564</v>
+        <v>-26.43630952478959</v>
       </c>
       <c r="F55">
-        <v>1.147415445842436</v>
+        <v>-0.2140859039292204</v>
       </c>
       <c r="G55">
-        <v>-10.59638869167647</v>
+        <v>-11.86678074746194</v>
       </c>
     </row>
     <row r="56" spans="1:7">
@@ -1668,13 +1668,13 @@
         <v>-16.64416954874072</v>
       </c>
       <c r="E56">
-        <v>-23.77679561024688</v>
+        <v>-26.03782645448463</v>
       </c>
       <c r="F56">
-        <v>1.162597763600945</v>
+        <v>-0.0399697027999867</v>
       </c>
       <c r="G56">
-        <v>-10.99609071790592</v>
+        <v>-11.99622969913852</v>
       </c>
     </row>
     <row r="57" spans="1:7">
@@ -1691,13 +1691,13 @@
         <v>-16.82646257492665</v>
       </c>
       <c r="E57">
-        <v>-25.13436871911035</v>
+        <v>-25.03440718386503</v>
       </c>
       <c r="F57">
-        <v>1.186636985630187</v>
+        <v>-0.05574761672110888</v>
       </c>
       <c r="G57">
-        <v>-9.092252257545224</v>
+        <v>-11.97071532466735</v>
       </c>
     </row>
     <row r="58" spans="1:7">
@@ -1714,13 +1714,13 @@
         <v>-17.03454155326879</v>
       </c>
       <c r="E58">
-        <v>-23.52845409566624</v>
+        <v>-24.99387734149638</v>
       </c>
       <c r="F58">
-        <v>0.9744059435633423</v>
+        <v>0.03696657646982299</v>
       </c>
       <c r="G58">
-        <v>-10.05156228064199</v>
+        <v>-12.01881755135297</v>
       </c>
     </row>
     <row r="59" spans="1:7">
@@ -1737,13 +1737,13 @@
         <v>-17.26720258589213</v>
       </c>
       <c r="E59">
-        <v>-24.29708557441015</v>
+        <v>-25.25592201842424</v>
       </c>
       <c r="F59">
-        <v>0.9692866330140414</v>
+        <v>0.154895445034569</v>
       </c>
       <c r="G59">
-        <v>-10.84328917799532</v>
+        <v>-12.46916761378772</v>
       </c>
     </row>
     <row r="60" spans="1:7">
@@ -1760,13 +1760,13 @@
         <v>-17.51814601469678</v>
       </c>
       <c r="E60">
-        <v>-22.45107578755337</v>
+        <v>-25.1982202026185</v>
       </c>
       <c r="F60">
-        <v>0.9010225320841397</v>
+        <v>-0.03692793769690692</v>
       </c>
       <c r="G60">
-        <v>-12.24349434546668</v>
+        <v>-12.72208005080588</v>
       </c>
     </row>
     <row r="61" spans="1:7">
@@ -1783,13 +1783,13 @@
         <v>-17.77497100799276</v>
       </c>
       <c r="E61">
-        <v>-23.58352033959951</v>
+        <v>-24.94472075614312</v>
       </c>
       <c r="F61">
-        <v>1.147654015654442</v>
+        <v>0.1574111968368711</v>
       </c>
       <c r="G61">
-        <v>-11.31514785479872</v>
+        <v>-12.84912885696649</v>
       </c>
     </row>
     <row r="62" spans="1:7">
@@ -1806,13 +1806,13 @@
         <v>-18.03529028994667</v>
       </c>
       <c r="E62">
-        <v>-23.24933707172947</v>
+        <v>-24.87774009709567</v>
       </c>
       <c r="F62">
-        <v>1.207564859694514</v>
+        <v>-0.08824529830033628</v>
       </c>
       <c r="G62">
-        <v>-11.42064832004421</v>
+        <v>-13.26940261317697</v>
       </c>
     </row>
     <row r="63" spans="1:7">
@@ -1829,13 +1829,13 @@
         <v>-18.29105838728568</v>
       </c>
       <c r="E63">
-        <v>-23.05563159605137</v>
+        <v>-24.72078318798982</v>
       </c>
       <c r="F63">
-        <v>0.6024391584798635</v>
+        <v>0.008995094379492079</v>
       </c>
       <c r="G63">
-        <v>-10.07735474093846</v>
+        <v>-12.7071097638773</v>
       </c>
     </row>
     <row r="64" spans="1:7">
@@ -1852,13 +1852,13 @@
         <v>-18.52891179887103</v>
       </c>
       <c r="E64">
-        <v>-22.66155020248187</v>
+        <v>-24.20860824924829</v>
       </c>
       <c r="F64">
-        <v>0.8978929600363632</v>
+        <v>0.05650527839965493</v>
       </c>
       <c r="G64">
-        <v>-12.16054200588916</v>
+        <v>-12.66309275038715</v>
       </c>
     </row>
     <row r="65" spans="1:7">
@@ -1875,13 +1875,13 @@
         <v>-18.74650060639913</v>
       </c>
       <c r="E65">
-        <v>-23.85467177775679</v>
+        <v>-23.70915379399431</v>
       </c>
       <c r="F65">
-        <v>1.129151601345512</v>
+        <v>0.02267475366932312</v>
       </c>
       <c r="G65">
-        <v>-10.90629217015319</v>
+        <v>-12.66765137159472</v>
       </c>
     </row>
     <row r="66" spans="1:7">
@@ -1898,13 +1898,13 @@
         <v>-18.93514826943296</v>
       </c>
       <c r="E66">
-        <v>-22.17900506917254</v>
+        <v>-24.56316965015285</v>
       </c>
       <c r="F66">
-        <v>1.167261472078706</v>
+        <v>-0.06339344784894832</v>
       </c>
       <c r="G66">
-        <v>-10.30376295036921</v>
+        <v>-13.07832785628685</v>
       </c>
     </row>
     <row r="67" spans="1:7">
@@ -1921,13 +1921,13 @@
         <v>-19.08280185436297</v>
       </c>
       <c r="E67">
-        <v>-22.56247171966805</v>
+        <v>-23.98449407060868</v>
       </c>
       <c r="F67">
-        <v>0.8256742331254967</v>
+        <v>-0.2796793483524964</v>
       </c>
       <c r="G67">
-        <v>-11.19375014987364</v>
+        <v>-12.52090150892991</v>
       </c>
     </row>
     <row r="68" spans="1:7">
@@ -1944,13 +1944,13 @@
         <v>-19.1897728392778</v>
       </c>
       <c r="E68">
-        <v>-21.33866520451716</v>
+        <v>-23.66190822467228</v>
       </c>
       <c r="F68">
-        <v>1.018943945342261</v>
+        <v>-0.1758815993121072</v>
       </c>
       <c r="G68">
-        <v>-12.30775865547501</v>
+        <v>-12.89400330175131</v>
       </c>
     </row>
     <row r="69" spans="1:7">
@@ -1967,13 +1967,13 @@
         <v>-19.24960947677454</v>
       </c>
       <c r="E69">
-        <v>-21.67309753845763</v>
+        <v>-24.11926145707695</v>
       </c>
       <c r="F69">
-        <v>0.6671561901909777</v>
+        <v>0.0523601279160462</v>
       </c>
       <c r="G69">
-        <v>-12.04805297901027</v>
+        <v>-13.4473278831851</v>
       </c>
     </row>
     <row r="70" spans="1:7">
@@ -1990,13 +1990,13 @@
         <v>-19.25570411190741</v>
       </c>
       <c r="E70">
-        <v>-22.55012709952315</v>
+        <v>-23.45813595127514</v>
       </c>
       <c r="F70">
-        <v>0.9345432474058245</v>
+        <v>-0.1115472733410864</v>
       </c>
       <c r="G70">
-        <v>-12.21062393880726</v>
+        <v>-12.6339632601871</v>
       </c>
     </row>
     <row r="71" spans="1:7">
@@ -2013,13 +2013,13 @@
         <v>-19.21413837589528</v>
       </c>
       <c r="E71">
-        <v>-22.82695724408604</v>
+        <v>-23.32860800923374</v>
       </c>
       <c r="F71">
-        <v>0.7231339458025571</v>
+        <v>-0.01614834139768132</v>
       </c>
       <c r="G71">
-        <v>-11.62406810125027</v>
+        <v>-12.80307916851523</v>
       </c>
     </row>
     <row r="72" spans="1:7">
@@ -2036,13 +2036,13 @@
         <v>-19.12271576448293</v>
       </c>
       <c r="E72">
-        <v>-23.2564377189735</v>
+        <v>-23.71405813134462</v>
       </c>
       <c r="F72">
-        <v>0.2022672916984643</v>
+        <v>-0.3751329525444863</v>
       </c>
       <c r="G72">
-        <v>-11.8202444088164</v>
+        <v>-12.46948211561395</v>
       </c>
     </row>
     <row r="73" spans="1:7">
@@ -2059,13 +2059,13 @@
         <v>-18.98086403363334</v>
       </c>
       <c r="E73">
-        <v>-21.68629804018999</v>
+        <v>-23.78939382493622</v>
       </c>
       <c r="F73">
-        <v>0.8832424541504511</v>
+        <v>-0.3137045394224861</v>
       </c>
       <c r="G73">
-        <v>-11.41154100926568</v>
+        <v>-12.68276070143596</v>
       </c>
     </row>
     <row r="74" spans="1:7">
@@ -2082,13 +2082,13 @@
         <v>-18.79983067262354</v>
       </c>
       <c r="E74">
-        <v>-22.54458877581176</v>
+        <v>-24.19012754682299</v>
       </c>
       <c r="F74">
-        <v>0.7294792401080012</v>
+        <v>-0.4780832817318116</v>
       </c>
       <c r="G74">
-        <v>-11.13230311411923</v>
+        <v>-12.52091475111207</v>
       </c>
     </row>
     <row r="75" spans="1:7">
@@ -2105,13 +2105,13 @@
         <v>-18.58045476727435</v>
       </c>
       <c r="E75">
-        <v>-22.29618839106902</v>
+        <v>-23.71122330661582</v>
       </c>
       <c r="F75">
-        <v>0.7071605371743742</v>
+        <v>-0.4804333600535538</v>
       </c>
       <c r="G75">
-        <v>-11.19865637836284</v>
+        <v>-12.37458532773074</v>
       </c>
     </row>
     <row r="76" spans="1:7">
@@ -2128,13 +2128,13 @@
         <v>-18.32676760060771</v>
       </c>
       <c r="E76">
-        <v>-24.71474673213759</v>
+        <v>-24.61726680064848</v>
       </c>
       <c r="F76">
-        <v>0.7414143576475366</v>
+        <v>-0.08818317074512633</v>
       </c>
       <c r="G76">
-        <v>-10.94895185997223</v>
+        <v>-12.15919461385468</v>
       </c>
     </row>
     <row r="77" spans="1:7">
@@ -2151,13 +2151,13 @@
         <v>-18.05325754187494</v>
       </c>
       <c r="E77">
-        <v>-23.22261454661021</v>
+        <v>-24.60397572943597</v>
       </c>
       <c r="F77">
-        <v>0.08847363320849344</v>
+        <v>-0.6508028554199253</v>
       </c>
       <c r="G77">
-        <v>-11.480820795766</v>
+        <v>-12.96481918138186</v>
       </c>
     </row>
     <row r="78" spans="1:7">
@@ -2174,13 +2174,13 @@
         <v>-17.76260232907806</v>
       </c>
       <c r="E78">
-        <v>-25.32135846783507</v>
+        <v>-24.32277107898166</v>
       </c>
       <c r="F78">
-        <v>0.4469587388114103</v>
+        <v>-0.4744144425048126</v>
       </c>
       <c r="G78">
-        <v>-11.11051310337975</v>
+        <v>-12.13327304228219</v>
       </c>
     </row>
     <row r="79" spans="1:7">
@@ -2197,13 +2197,13 @@
         <v>-17.46214876800023</v>
       </c>
       <c r="E79">
-        <v>-25.56388995026387</v>
+        <v>-25.49840821611296</v>
       </c>
       <c r="F79">
-        <v>0.3044372987923525</v>
+        <v>-0.5760352420106447</v>
       </c>
       <c r="G79">
-        <v>-10.47264049941851</v>
+        <v>-12.51698182301141</v>
       </c>
     </row>
     <row r="80" spans="1:7">
@@ -2220,13 +2220,13 @@
         <v>-17.16832178489961</v>
       </c>
       <c r="E80">
-        <v>-24.75642227843018</v>
+        <v>-25.99701584672751</v>
       </c>
       <c r="F80">
-        <v>0.1958159663654618</v>
+        <v>-0.1615897765116073</v>
       </c>
       <c r="G80">
-        <v>-10.31279411860034</v>
+        <v>-12.29091128922566</v>
       </c>
     </row>
     <row r="81" spans="1:7">
@@ -2243,13 +2243,13 @@
         <v>-16.88341491886073</v>
       </c>
       <c r="E81">
-        <v>-25.95078012710919</v>
+        <v>-25.98321305795213</v>
       </c>
       <c r="F81">
-        <v>0.8222215977906283</v>
+        <v>-0.7251662255366398</v>
       </c>
       <c r="G81">
-        <v>-10.89688691027612</v>
+        <v>-12.13305785682213</v>
       </c>
     </row>
     <row r="82" spans="1:7">
@@ -2266,13 +2266,13 @@
         <v>-16.61312426119422</v>
       </c>
       <c r="E82">
-        <v>-25.82736109650414</v>
+        <v>-26.58429552688624</v>
       </c>
       <c r="F82">
-        <v>0.2953998104278099</v>
+        <v>-0.6395643948661445</v>
       </c>
       <c r="G82">
-        <v>-11.39026744363032</v>
+        <v>-11.62452164598915</v>
       </c>
     </row>
     <row r="83" spans="1:7">
@@ -2289,13 +2289,13 @@
         <v>-16.37185537269775</v>
       </c>
       <c r="E83">
-        <v>-25.76671577259342</v>
+        <v>-27.66175534753125</v>
       </c>
       <c r="F83">
-        <v>0.7649482755610705</v>
+        <v>-0.8894049737548921</v>
       </c>
       <c r="G83">
-        <v>-10.10431251326474</v>
+        <v>-11.65083386193528</v>
       </c>
     </row>
     <row r="84" spans="1:7">
@@ -2312,13 +2312,13 @@
         <v>-16.15909430784104</v>
       </c>
       <c r="E84">
-        <v>-27.78422339859469</v>
+        <v>-28.51694860693178</v>
       </c>
       <c r="F84">
-        <v>0.4378408988087961</v>
+        <v>-0.9116971689316297</v>
       </c>
       <c r="G84">
-        <v>-10.50880820943505</v>
+        <v>-11.42672317110877</v>
       </c>
     </row>
     <row r="85" spans="1:7">
@@ -2335,13 +2335,13 @@
         <v>-15.97799109643742</v>
       </c>
       <c r="E85">
-        <v>-28.38191856897107</v>
+        <v>-28.96402673181305</v>
       </c>
       <c r="F85">
-        <v>0.373375690788133</v>
+        <v>-0.9420038187304524</v>
       </c>
       <c r="G85">
-        <v>-9.428696379610278</v>
+        <v>-11.28831257265738</v>
       </c>
     </row>
     <row r="86" spans="1:7">
@@ -2358,13 +2358,13 @@
         <v>-15.84164499328364</v>
       </c>
       <c r="E86">
-        <v>-28.99787254654638</v>
+        <v>-29.2381171496013</v>
       </c>
       <c r="F86">
-        <v>0.02011427002726984</v>
+        <v>-1.035446975235848</v>
       </c>
       <c r="G86">
-        <v>-10.52742671754791</v>
+        <v>-10.84178287977495</v>
       </c>
     </row>
     <row r="87" spans="1:7">
@@ -2381,13 +2381,13 @@
         <v>-15.74902492951058</v>
       </c>
       <c r="E87">
-        <v>-30.00596520234189</v>
+        <v>-30.45514453916271</v>
       </c>
       <c r="F87">
-        <v>-0.4163384322619421</v>
+        <v>-1.240766948061136</v>
       </c>
       <c r="G87">
-        <v>-9.921106923121473</v>
+        <v>-11.06496992839599</v>
       </c>
     </row>
     <row r="88" spans="1:7">
@@ -2404,13 +2404,13 @@
         <v>-15.70153760050674</v>
       </c>
       <c r="E88">
-        <v>-30.62011231878813</v>
+        <v>-31.06541301762139</v>
       </c>
       <c r="F88">
-        <v>-0.179274592193974</v>
+        <v>-0.9150122952776333</v>
       </c>
       <c r="G88">
-        <v>-9.585093171976526</v>
+        <v>-11.55490087329828</v>
       </c>
     </row>
     <row r="89" spans="1:7">
@@ -2427,13 +2427,13 @@
         <v>-15.7130438225203</v>
       </c>
       <c r="E89">
-        <v>-33.96426131194347</v>
+        <v>-31.73770574032612</v>
       </c>
       <c r="F89">
-        <v>0.147892427011302</v>
+        <v>-1.148346825298198</v>
       </c>
       <c r="G89">
-        <v>-9.484969032686809</v>
+        <v>-10.69432456036473</v>
       </c>
     </row>
     <row r="90" spans="1:7">
@@ -2450,13 +2450,13 @@
         <v>-15.7817492030038</v>
       </c>
       <c r="E90">
-        <v>-34.24337833588024</v>
+        <v>-33.61620279971393</v>
       </c>
       <c r="F90">
-        <v>0.03043241439654049</v>
+        <v>-1.308837211018783</v>
       </c>
       <c r="G90">
-        <v>-9.843620294229291</v>
+        <v>-10.56736513893368</v>
       </c>
     </row>
     <row r="91" spans="1:7">
@@ -2473,13 +2473,13 @@
         <v>-15.90523704694328</v>
       </c>
       <c r="E91">
-        <v>-34.03397037658055</v>
+        <v>-34.4570158899031</v>
       </c>
       <c r="F91">
-        <v>0.01492786171834214</v>
+        <v>-1.44953292928207</v>
       </c>
       <c r="G91">
-        <v>-8.387211995137719</v>
+        <v>-10.68271116661297</v>
       </c>
     </row>
     <row r="92" spans="1:7">
@@ -2496,13 +2496,13 @@
         <v>-16.09572220782055</v>
       </c>
       <c r="E92">
-        <v>-36.58660324759421</v>
+        <v>-35.91806915831584</v>
       </c>
       <c r="F92">
-        <v>0.2462063838451585</v>
+        <v>-1.559638696094778</v>
       </c>
       <c r="G92">
-        <v>-8.582736125232614</v>
+        <v>-10.62979209616772</v>
       </c>
     </row>
     <row r="93" spans="1:7">
@@ -2519,13 +2519,13 @@
         <v>-16.34801432672251</v>
       </c>
       <c r="E93">
-        <v>-37.52096328959684</v>
+        <v>-37.85105734543796</v>
       </c>
       <c r="F93">
-        <v>-0.3415989833443567</v>
+        <v>-1.689124946663382</v>
       </c>
       <c r="G93">
-        <v>-9.20746917394848</v>
+        <v>-10.61973134827387</v>
       </c>
     </row>
     <row r="94" spans="1:7">
@@ -2542,13 +2542,13 @@
         <v>-16.654003065053</v>
       </c>
       <c r="E94">
-        <v>-37.95658890371271</v>
+        <v>-39.87772833859374</v>
       </c>
       <c r="F94">
-        <v>-0.2863775271715333</v>
+        <v>-1.843620437489907</v>
       </c>
       <c r="G94">
-        <v>-8.85538934530145</v>
+        <v>-11.00969374952678</v>
       </c>
     </row>
     <row r="95" spans="1:7">
@@ -2565,13 +2565,13 @@
         <v>-17.02124141032713</v>
       </c>
       <c r="E95">
-        <v>-38.88019834842112</v>
+        <v>-40.94058609480102</v>
       </c>
       <c r="F95">
-        <v>-1.09504138292805</v>
+        <v>-1.843053005818989</v>
       </c>
       <c r="G95">
-        <v>-8.669439312906126</v>
+        <v>-11.00172195586822</v>
       </c>
     </row>
     <row r="96" spans="1:7">
@@ -2588,13 +2588,13 @@
         <v>-17.44260585159466</v>
       </c>
       <c r="E96">
-        <v>-42.38019930302444</v>
+        <v>-42.45267526528021</v>
       </c>
       <c r="F96">
-        <v>-0.8735558202371292</v>
+        <v>-2.263166989455384</v>
       </c>
       <c r="G96">
-        <v>-9.463175711401787</v>
+        <v>-11.06309284907523</v>
       </c>
     </row>
     <row r="97" spans="1:7">
@@ -2611,13 +2611,13 @@
         <v>-17.89854675294159</v>
       </c>
       <c r="E97">
-        <v>-44.59044557550317</v>
+        <v>-43.88709431381683</v>
       </c>
       <c r="F97">
-        <v>-0.8357383631971234</v>
+        <v>-2.244388728801322</v>
       </c>
       <c r="G97">
-        <v>-9.784149654161824</v>
+        <v>-10.82510766189364</v>
       </c>
     </row>
     <row r="98" spans="1:7">
@@ -2634,13 +2634,13 @@
         <v>-18.40359510702021</v>
       </c>
       <c r="E98">
-        <v>-46.7424194444512</v>
+        <v>-45.72574080193714</v>
       </c>
       <c r="F98">
-        <v>-2.156450073687529</v>
+        <v>-2.816016908981565</v>
       </c>
       <c r="G98">
-        <v>-9.371387525779953</v>
+        <v>-11.12279853787598</v>
       </c>
     </row>
     <row r="99" spans="1:7">
@@ -2657,13 +2657,13 @@
         <v>-18.92409566446545</v>
       </c>
       <c r="E99">
-        <v>-48.44780199947379</v>
+        <v>-46.90835405327726</v>
       </c>
       <c r="F99">
-        <v>-1.463843804532835</v>
+        <v>-2.539503728090077</v>
       </c>
       <c r="G99">
-        <v>-8.833877420387266</v>
+        <v>-11.15368923830292</v>
       </c>
     </row>
     <row r="100" spans="1:7">
@@ -2680,13 +2680,13 @@
         <v>-19.47162008633175</v>
       </c>
       <c r="E100">
-        <v>-49.37092916170039</v>
+        <v>-49.48655808489374</v>
       </c>
       <c r="F100">
-        <v>-1.555319588456581</v>
+        <v>-3.057050285643749</v>
       </c>
       <c r="G100">
-        <v>-10.88519406343141</v>
+        <v>-11.45971606795315</v>
       </c>
     </row>
     <row r="101" spans="1:7">
@@ -2703,13 +2703,13 @@
         <v>-20.00362067194919</v>
       </c>
       <c r="E101">
-        <v>-51.87091852237489</v>
+        <v>-50.83083785830769</v>
       </c>
       <c r="F101">
-        <v>-2.016447698940385</v>
+        <v>-2.952510319410451</v>
       </c>
       <c r="G101">
-        <v>-9.927161910912801</v>
+        <v>-11.44162724712657</v>
       </c>
     </row>
     <row r="102" spans="1:7">
@@ -2726,13 +2726,13 @@
         <v>-20.57792372317147</v>
       </c>
       <c r="E102">
-        <v>-52.77866472263443</v>
+        <v>-53.61375382167791</v>
       </c>
       <c r="F102">
-        <v>-2.441236159830777</v>
+        <v>-3.514974271013524</v>
       </c>
       <c r="G102">
-        <v>-10.55850611907059</v>
+        <v>-11.82640864461052</v>
       </c>
     </row>
   </sheetData>
